--- a/InputData/ctrl-settings/FYIbFP/First Year Impacted by Future Policies.xlsx
+++ b/InputData/ctrl-settings/FYIbFP/First Year Impacted by Future Policies.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanOBrien\Models\EPS\US\eps-us\InputData\ctrl-settings\FYIbFP\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\ctrl-settings\FYIbFP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E6FA6DE-B671-4527-B218-84831E0DC5C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2B6F6FB-271C-40C8-8DBE-5BACC4051760}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
-    <sheet name="BDCTBA" sheetId="2" r:id="rId2"/>
+    <sheet name="FYIbFP" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="145621"/>
 </workbook>
